--- a/tests/workbooktests/workbooks/test_calibratedmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_calibratedmodel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1126437-59EB-41FD-A5C7-6FC047C918C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6889E0-1D68-47A0-8ACF-903534D570DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13530" yWindow="-19245" windowWidth="23175" windowHeight="16410" xr2:uid="{2FEFDE40-9C41-44A1-8868-8F33D5CA59CC}"/>
+    <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" xr2:uid="{2FEFDE40-9C41-44A1-8868-8F33D5CA59CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,9 +546,9 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="2" t="e">
+        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -585,18 +563,18 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R6C2YieldTermStructureHandle,A</v>
+      <c r="B6" t="e">
+        <f ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward(B2,0.02)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R7C2YieldTermStructureHandle,A</v>
+      <c r="B7" t="e">
+        <f ca="1">_xll.qlFlatForward(B2,0.02)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -651,45 +629,45 @@
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B16" t="str" cm="1">
-        <f t="array" ref="B16">_xll.qlHestonProcess(B7,B6,B5,B10,B11,B12,B13,B14,B15)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R16C2HestonProcess,A</v>
+      <c r="B16" t="e">
+        <f ca="1">_xll.qlHestonProcess(B7,B6,B5,B10,B11,B12,B13,B14,B15,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="str" cm="1">
-        <f t="array" ref="B18">_xll.qlHestonModel(B16)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R18C2HestonModel,A</v>
+      <c r="B18" t="e">
+        <f ca="1">_xll.qlHestonModel(B16)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="str" cm="1">
-        <f t="array" ref="B19">_xll.qlAnalyticHestonEngine(B18)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R19C2AnalyticHestonEngine,A</v>
+      <c r="B19" t="e">
+        <f ca="1">_xll.qlAnalyticHestonEngine(B18)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="str" cm="1">
-        <f t="array" ref="B21">_xll.qlLevenbergMarquardt()</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R21C2LevenbergMarquardt,A</v>
+      <c r="B21" t="e">
+        <f ca="1">_xll.qlLevenbergMarquardt(,,,,B19)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" t="str" cm="1">
-        <f t="array" ref="B22">_xll.qlEndCriteria(100,10,0.000001,0.000001,0.000001)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R22C2EndCriteria,A</v>
+      <c r="B22" t="e">
+        <f ca="1">_xll.qlEndCriteria(100,10,0.000001,0.000001,0.000001,B21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -712,13 +690,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="b" cm="1">
-        <f t="array" ref="A27">_xll.qlBlackCalibrationHelperSetPricingEngine(B27,$B$19)</f>
-        <v>1</v>
-      </c>
-      <c r="B27" t="str" cm="1">
-        <f t="array" ref="B27">_xll.qlHestonModelHelper(C27,$B$24,$B$5,D27,E27,$B$7,$B$6)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R27C2HestonModelHelper,A</v>
+      <c r="A27" t="e">
+        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B27,$B$19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B27" t="e">
+        <f ca="1">_xll.qlHestonModelHelper(C27,$B$24,$B$5,D27,E27,$B$7,$B$6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -731,13 +709,13 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="b" cm="1">
-        <f t="array" ref="A28">_xll.qlBlackCalibrationHelperSetPricingEngine(B28,$B$19)</f>
-        <v>1</v>
-      </c>
-      <c r="B28" t="str" cm="1">
-        <f t="array" ref="B28">_xll.qlHestonModelHelper(C28,$B$24,$B$5,D28,E28,$B$7,$B$6)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R28C2HestonModelHelper,A</v>
+      <c r="A28" t="e">
+        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B28,$B$19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B28" t="e">
+        <f ca="1">_xll.qlHestonModelHelper(C28,$B$24,$B$5,D28,E28,$B$7,$B$6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
@@ -750,13 +728,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="b" cm="1">
-        <f t="array" ref="A29">_xll.qlBlackCalibrationHelperSetPricingEngine(B29,$B$19)</f>
-        <v>1</v>
-      </c>
-      <c r="B29" t="str" cm="1">
-        <f t="array" ref="B29">_xll.qlHestonModelHelper(C29,$B$24,$B$5,D29,E29,$B$7,$B$6)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R29C2HestonModelHelper,A</v>
+      <c r="A29" t="e">
+        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B29,$B$19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B29" t="e">
+        <f ca="1">_xll.qlHestonModelHelper(C29,$B$24,$B$5,D29,E29,$B$7,$B$6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -769,13 +747,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="b" cm="1">
-        <f t="array" ref="A30">_xll.qlBlackCalibrationHelperSetPricingEngine(B30,$B$19)</f>
-        <v>1</v>
-      </c>
-      <c r="B30" t="str" cm="1">
-        <f t="array" ref="B30">_xll.qlHestonModelHelper(C30,$B$24,$B$5,D30,E30,$B$7,$B$6)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R30C2HestonModelHelper,A</v>
+      <c r="A30" t="e">
+        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B30,$B$19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B30" t="e">
+        <f ca="1">_xll.qlHestonModelHelper(C30,$B$24,$B$5,D30,E30,$B$7,$B$6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
@@ -788,13 +766,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="b" cm="1">
-        <f t="array" ref="A31">_xll.qlBlackCalibrationHelperSetPricingEngine(B31,$B$19)</f>
-        <v>1</v>
-      </c>
-      <c r="B31" t="str" cm="1">
-        <f t="array" ref="B31">_xll.qlHestonModelHelper(C31,$B$24,$B$5,D31,E31,$B$7,$B$6)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R31C2HestonModelHelper,A</v>
+      <c r="A31" t="e">
+        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B31,$B$19)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B31" t="e">
+        <f ca="1">_xll.qlHestonModelHelper(C31,$B$24,$B$5,D31,E31,$B$7,$B$6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -810,70 +788,58 @@
       <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="B33" t="str" cm="1">
-        <f t="array" ref="B33">_xll.qlCalibratedModelCalibrate(B18,B27:B31,B21,B22,,,,A27:A31)</f>
-        <v>Error in arg 3 'optimization_method': Cannot convert '⚡[test_calibratedmodel.xlsx]Sheet1!R21C2LevenbergMarquardt,A': Expected cache string</v>
+      <c r="B33" t="e">
+        <f ca="1">_xll.qlCalibratedModelCalibrate(B18,B27:B31,B21,B22,,,,A27:A31)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" cm="1">
-        <f t="array" ref="B36:B40">_xll.qlCalibratedModelParams(B18,B33)</f>
-        <v>0.04</v>
-      </c>
-      <c r="D36" cm="1">
-        <f t="array" ref="D36">_xll.qlHestonModelTheta(B18,B33)</f>
-        <v>0.04</v>
+      <c r="B36" t="e">
+        <f ca="1">_xll.qlCalibratedModelParams(B18,B33)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D36" t="e">
+        <f ca="1">_xll.qlHestonModelTheta(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37">
-        <v>1.5</v>
-      </c>
-      <c r="D37" cm="1">
-        <f t="array" ref="D37">_xll.qlHestonModelKappa(B18,B33)</f>
-        <v>1.5</v>
+      <c r="D37" t="e">
+        <f ca="1">_xll.qlHestonModelKappa(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B38">
-        <v>0.3</v>
-      </c>
-      <c r="D38" cm="1">
-        <f t="array" ref="D38">_xll.qlHestonModelSigma(B18,B33)</f>
-        <v>0.3</v>
+      <c r="D38" t="e">
+        <f ca="1">_xll.qlHestonModelSigma(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39">
-        <v>-0.7</v>
-      </c>
-      <c r="D39" cm="1">
-        <f t="array" ref="D39">_xll.qlHestonModelRho(B18,B33)</f>
-        <v>-0.7</v>
+      <c r="D39" t="e">
+        <f ca="1">_xll.qlHestonModelRho(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B40">
-        <v>0.04</v>
-      </c>
-      <c r="D40" cm="1">
-        <f t="array" ref="D40">_xll.qlHestonModelV0(B18,B33)</f>
-        <v>0.04</v>
+      <c r="D40" t="e">
+        <f ca="1">_xll.qlHestonModelV0(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E40" t="s">
         <v>34</v>
@@ -883,27 +849,27 @@
       <c r="A42" t="s">
         <v>24</v>
       </c>
-      <c r="B42" cm="1">
-        <f t="array" ref="B42">_xll.qlCalibratedModelProblemValues(B18,B33)</f>
-        <v>0</v>
+      <c r="B42" t="e">
+        <f ca="1">_xll.qlCalibratedModelProblemValues(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
-      <c r="B48" cm="1">
-        <f t="array" ref="B48">_xll.qlCalibratedModelProblemValuesFunctionEvaluation(B18,B33)</f>
-        <v>115563376</v>
+      <c r="B48" t="e">
+        <f ca="1">_xll.qlCalibratedModelProblemValuesFunctionEvaluation(B18,B33)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
-      <c r="B50" t="str" cm="1">
-        <f t="array" ref="B50">_xll.qlCalibratedModelHandle(B18)</f>
-        <v>⚡[test_calibratedmodel.xlsx]Sheet1!R50C2CalibratedModelHandle,A</v>
+      <c r="B50" t="e">
+        <f ca="1">_xll.qlCalibratedModelHandle(B18)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
